--- a/data-source/battlepass.template.xlsx
+++ b/data-source/battlepass.template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <sheets>
     <sheet name="pvp" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -490,6 +490,7 @@
         <v>0</v>
       </c>
       <c r="O2">
+        <f>SUM(F2:N2)</f>
         <v>1</v>
       </c>
     </row>
@@ -537,6 +538,7 @@
         <v>0</v>
       </c>
       <c r="O3">
+        <f>SUM(F3:N3)</f>
         <v>3</v>
       </c>
     </row>
@@ -584,6 +586,7 @@
         <v>0</v>
       </c>
       <c r="O4">
+        <f>SUM(F4:N4)</f>
         <v>3</v>
       </c>
     </row>
@@ -631,6 +634,7 @@
         <v>0</v>
       </c>
       <c r="O5">
+        <f>SUM(F5:N5)</f>
         <v>3</v>
       </c>
     </row>
@@ -678,6 +682,7 @@
         <v>0</v>
       </c>
       <c r="O6">
+        <f>SUM(F6:N6)</f>
         <v>5</v>
       </c>
     </row>
@@ -725,6 +730,7 @@
         <v>0</v>
       </c>
       <c r="O7">
+        <f>SUM(F7:N7)</f>
         <v>4</v>
       </c>
     </row>
@@ -772,6 +778,7 @@
         <v>0</v>
       </c>
       <c r="O8">
+        <f>SUM(F8:N8)</f>
         <v>7</v>
       </c>
     </row>
@@ -819,6 +826,7 @@
         <v>0</v>
       </c>
       <c r="O9">
+        <f>SUM(F9:N9)</f>
         <v>3</v>
       </c>
     </row>
@@ -866,6 +874,7 @@
         <v>0</v>
       </c>
       <c r="O10">
+        <f>SUM(F10:N10)</f>
         <v>3</v>
       </c>
     </row>
@@ -913,6 +922,7 @@
         <v>0</v>
       </c>
       <c r="O11">
+        <f>SUM(F11:N11)</f>
         <v>3</v>
       </c>
     </row>
@@ -960,6 +970,7 @@
         <v>0</v>
       </c>
       <c r="O12">
+        <f>SUM(F12:N12)</f>
         <v>4</v>
       </c>
     </row>
@@ -1007,6 +1018,7 @@
         <v>0</v>
       </c>
       <c r="O13">
+        <f>SUM(F13:N13)</f>
         <v>5</v>
       </c>
     </row>
@@ -1054,6 +1066,7 @@
         <v>0</v>
       </c>
       <c r="O14">
+        <f>SUM(F14:N14)</f>
         <v>7</v>
       </c>
     </row>
@@ -1101,6 +1114,7 @@
         <v>0</v>
       </c>
       <c r="O15">
+        <f>SUM(F15:N15)</f>
         <v>5</v>
       </c>
     </row>
@@ -1148,6 +1162,7 @@
         <v>0</v>
       </c>
       <c r="O16">
+        <f>SUM(F16:N16)</f>
         <v>4</v>
       </c>
     </row>
@@ -1195,6 +1210,7 @@
         <v>0</v>
       </c>
       <c r="O17">
+        <f>SUM(F17:N17)</f>
         <v>5</v>
       </c>
     </row>
@@ -1242,6 +1258,7 @@
         <v>0</v>
       </c>
       <c r="O18">
+        <f>SUM(F18:N18)</f>
         <v>10</v>
       </c>
     </row>
@@ -1289,6 +1306,7 @@
         <v>0</v>
       </c>
       <c r="O19">
+        <f>SUM(F19:N19)</f>
         <v>5</v>
       </c>
     </row>
@@ -1336,6 +1354,7 @@
         <v>0</v>
       </c>
       <c r="O20">
+        <f>SUM(F20:N20)</f>
         <v>5</v>
       </c>
     </row>
@@ -1383,6 +1402,7 @@
         <v>0</v>
       </c>
       <c r="O21">
+        <f>SUM(F21:N21)</f>
         <v>5</v>
       </c>
     </row>
@@ -1430,6 +1450,7 @@
         <v>0</v>
       </c>
       <c r="O22">
+        <f>SUM(F22:N22)</f>
         <v>10</v>
       </c>
     </row>
@@ -1477,6 +1498,7 @@
         <v>0</v>
       </c>
       <c r="O23">
+        <f>SUM(F23:N23)</f>
         <v>7</v>
       </c>
     </row>
@@ -1524,6 +1546,7 @@
         <v>0</v>
       </c>
       <c r="O24">
+        <f>SUM(F24:N24)</f>
         <v>5</v>
       </c>
     </row>
@@ -1571,6 +1594,7 @@
         <v>0</v>
       </c>
       <c r="O25">
+        <f>SUM(F25:N25)</f>
         <v>6</v>
       </c>
     </row>
@@ -1618,6 +1642,7 @@
         <v>0</v>
       </c>
       <c r="O26">
+        <f>SUM(F26:N26)</f>
         <v>7</v>
       </c>
     </row>
@@ -1665,6 +1690,7 @@
         <v>0</v>
       </c>
       <c r="O27">
+        <f>SUM(F27:N27)</f>
         <v>13</v>
       </c>
     </row>
@@ -1712,6 +1738,7 @@
         <v>0</v>
       </c>
       <c r="O28">
+        <f>SUM(F28:N28)</f>
         <v>12</v>
       </c>
     </row>
@@ -1759,6 +1786,7 @@
         <v>0</v>
       </c>
       <c r="O29">
+        <f>SUM(F29:N29)</f>
         <v>11</v>
       </c>
     </row>
@@ -1806,6 +1834,7 @@
         <v>0</v>
       </c>
       <c r="O30">
+        <f>SUM(F30:N30)</f>
         <v>10</v>
       </c>
     </row>
@@ -1853,6 +1882,7 @@
         <v>0</v>
       </c>
       <c r="O31">
+        <f>SUM(F31:N31)</f>
         <v>9</v>
       </c>
     </row>
@@ -1900,6 +1930,7 @@
         <v>0</v>
       </c>
       <c r="O32">
+        <f>SUM(F32:N32)</f>
         <v>13</v>
       </c>
     </row>
@@ -1947,6 +1978,7 @@
         <v>0</v>
       </c>
       <c r="O33">
+        <f>SUM(F33:N33)</f>
         <v>13</v>
       </c>
     </row>
@@ -1994,6 +2026,7 @@
         <v>0</v>
       </c>
       <c r="O34">
+        <f>SUM(F34:N34)</f>
         <v>6</v>
       </c>
     </row>
@@ -2041,6 +2074,7 @@
         <v>0</v>
       </c>
       <c r="O35">
+        <f>SUM(F35:N35)</f>
         <v>14</v>
       </c>
     </row>
@@ -2088,6 +2122,7 @@
         <v>0</v>
       </c>
       <c r="O36">
+        <f>SUM(F36:N36)</f>
         <v>13</v>
       </c>
     </row>
@@ -2135,6 +2170,7 @@
         <v>0</v>
       </c>
       <c r="O37">
+        <f>SUM(F37:N37)</f>
         <v>6</v>
       </c>
     </row>
@@ -2182,6 +2218,7 @@
         <v>0</v>
       </c>
       <c r="O38">
+        <f>SUM(F38:N38)</f>
         <v>4</v>
       </c>
     </row>
@@ -2229,6 +2266,7 @@
         <v>0</v>
       </c>
       <c r="O39">
+        <f>SUM(F39:N39)</f>
         <v>12</v>
       </c>
     </row>
@@ -2276,6 +2314,7 @@
         <v>0</v>
       </c>
       <c r="O40">
+        <f>SUM(F40:N40)</f>
         <v>6</v>
       </c>
     </row>
@@ -2323,6 +2362,7 @@
         <v>0</v>
       </c>
       <c r="O41">
+        <f>SUM(F41:N41)</f>
         <v>9</v>
       </c>
     </row>
@@ -2370,6 +2410,7 @@
         <v>0</v>
       </c>
       <c r="O42">
+        <f>SUM(F42:N42)</f>
         <v>5</v>
       </c>
     </row>
@@ -2417,6 +2458,7 @@
         <v>0</v>
       </c>
       <c r="O43">
+        <f>SUM(F43:N43)</f>
         <v>18</v>
       </c>
     </row>
@@ -2464,6 +2506,7 @@
         <v>0</v>
       </c>
       <c r="O44">
+        <f>SUM(F44:N44)</f>
         <v>20</v>
       </c>
     </row>
@@ -2511,6 +2554,7 @@
         <v>0</v>
       </c>
       <c r="O45">
+        <f>SUM(F45:N45)</f>
         <v>20</v>
       </c>
     </row>
@@ -2558,6 +2602,7 @@
         <v>0</v>
       </c>
       <c r="O46">
+        <f>SUM(F46:N46)</f>
         <v>7</v>
       </c>
     </row>
@@ -2605,6 +2650,7 @@
         <v>0</v>
       </c>
       <c r="O47">
+        <f>SUM(F47:N47)</f>
         <v>13</v>
       </c>
     </row>
@@ -2652,6 +2698,7 @@
         <v>0</v>
       </c>
       <c r="O48">
+        <f>SUM(F48:N48)</f>
         <v>11</v>
       </c>
     </row>
@@ -2699,6 +2746,7 @@
         <v>0</v>
       </c>
       <c r="O49">
+        <f>SUM(F49:N49)</f>
         <v>16</v>
       </c>
     </row>
@@ -2746,6 +2794,7 @@
         <v>0</v>
       </c>
       <c r="O50">
+        <f>SUM(F50:N50)</f>
         <v>19</v>
       </c>
     </row>
@@ -2793,6 +2842,7 @@
         <v>0</v>
       </c>
       <c r="O51">
+        <f>SUM(F51:N51)</f>
         <v>19</v>
       </c>
     </row>
@@ -2840,6 +2890,7 @@
         <v>0</v>
       </c>
       <c r="O52">
+        <f>SUM(F52:N52)</f>
         <v>29</v>
       </c>
     </row>
@@ -2887,6 +2938,7 @@
         <v>0</v>
       </c>
       <c r="O53">
+        <f>SUM(F53:N53)</f>
         <v>25</v>
       </c>
     </row>
@@ -2934,6 +2986,7 @@
         <v>0</v>
       </c>
       <c r="O54">
+        <f>SUM(F54:N54)</f>
         <v>23</v>
       </c>
     </row>
@@ -2966,10 +3019,12 @@
         <v>0</v>
       </c>
       <c r="O55">
+        <f>SUM(O2:O54)</f>
         <v>501</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:O55"/>
   </ignoredErrors>

--- a/data-source/battlepass.template.xlsx
+++ b/data-source/battlepass.template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="pvp" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,34 +413,34 @@
         <v>Item Name</v>
       </c>
       <c r="E1" t="str">
-        <v>Type</v>
+        <v>Financial documents</v>
       </c>
       <c r="F1" t="str">
-        <v>Blueprints and technical documentation</v>
+        <v>PMC personell files</v>
       </c>
       <c r="G1" t="str">
         <v>Project documentation</v>
       </c>
       <c r="H1" t="str">
-        <v>Financial documents</v>
+        <v>Blueprints and technical documentation</v>
       </c>
       <c r="I1" t="str">
-        <v>PMC personell files</v>
+        <v>Test documentation</v>
       </c>
       <c r="J1" t="str">
+        <v>User documentation</v>
+      </c>
+      <c r="K1" t="str">
         <v>Medical documents</v>
       </c>
-      <c r="K1" t="str">
-        <v>User documentation</v>
-      </c>
       <c r="L1" t="str">
-        <v>Test documentation</v>
+        <v>Technical documentation</v>
       </c>
       <c r="M1" t="str">
-        <v>Technical documentation</v>
+        <v>Classified documents</v>
       </c>
       <c r="N1" t="str">
-        <v>Classified documents</v>
+        <v>Doc Count</v>
       </c>
       <c r="O1" t="str">
         <v>Total Documents</v>
@@ -459,8 +459,8 @@
       <c r="D2" t="str">
         <v>marked_dogtag_grey</v>
       </c>
-      <c r="E2" t="str">
-        <v>dogtag</v>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -487,10 +487,10 @@
         <v>0</v>
       </c>
       <c r="N2">
+        <f>SUM(E2:M2)</f>
         <v>0</v>
       </c>
       <c r="O2">
-        <f>SUM(F2:N2)</f>
         <v>1</v>
       </c>
     </row>
@@ -507,8 +507,8 @@
       <c r="D3" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E3" t="str">
-        <v>currency</v>
+      <c r="E3">
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -535,10 +535,10 @@
         <v>0</v>
       </c>
       <c r="N3">
+        <f>SUM(E3:M3)</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>SUM(F3:N3)</f>
         <v>3</v>
       </c>
     </row>
@@ -555,8 +555,8 @@
       <c r="D4" t="str">
         <v>burn_poster</v>
       </c>
-      <c r="E4" t="str">
-        <v>poster</v>
+      <c r="E4">
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -583,10 +583,10 @@
         <v>0</v>
       </c>
       <c r="N4">
+        <f>SUM(E4:M4)</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>SUM(F4:N4)</f>
         <v>3</v>
       </c>
     </row>
@@ -603,8 +603,8 @@
       <c r="D5" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E5" t="str">
-        <v>loot container</v>
+      <c r="E5">
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -631,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="N5">
+        <f>SUM(E5:M5)</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>SUM(F5:N5)</f>
         <v>3</v>
       </c>
     </row>
@@ -651,8 +651,8 @@
       <c r="D6" t="str">
         <v>black_wood_ceiling</v>
       </c>
-      <c r="E6" t="str">
-        <v>hideout customization</v>
+      <c r="E6">
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="N6">
+        <f>SUM(E6:M6)</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>SUM(F6:N6)</f>
         <v>5</v>
       </c>
     </row>
@@ -699,8 +699,8 @@
       <c r="D7" t="str">
         <v>gentex_ops-core_sotr_respirator</v>
       </c>
-      <c r="E7" t="str">
-        <v>trade offer</v>
+      <c r="E7">
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -727,10 +727,10 @@
         <v>0</v>
       </c>
       <c r="N7">
+        <f>SUM(E7:M7)</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>SUM(F7:N7)</f>
         <v>4</v>
       </c>
     </row>
@@ -747,8 +747,8 @@
       <c r="D8" t="str">
         <v>red_hawaii</v>
       </c>
-      <c r="E8" t="str">
-        <v>tactical clothing</v>
+      <c r="E8">
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -775,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="N8">
+        <f>SUM(E8:M8)</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>SUM(F8:N8)</f>
         <v>7</v>
       </c>
     </row>
@@ -795,8 +795,8 @@
       <c r="D9" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E9" t="str">
-        <v>loot container</v>
+      <c r="E9">
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="N9">
+        <f>SUM(E9:M9)</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>SUM(F9:N9)</f>
         <v>3</v>
       </c>
     </row>
@@ -843,8 +843,8 @@
       <c r="D10" t="str">
         <v>scorpion_target</v>
       </c>
-      <c r="E10" t="str">
-        <v>hideout customization</v>
+      <c r="E10">
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -871,10 +871,10 @@
         <v>0</v>
       </c>
       <c r="N10">
+        <f>SUM(E10:M10)</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>SUM(F10:N10)</f>
         <v>3</v>
       </c>
     </row>
@@ -891,8 +891,8 @@
       <c r="D11" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E11" t="str">
-        <v>currency</v>
+      <c r="E11">
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -919,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="N11">
+        <f>SUM(E11:M11)</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>SUM(F11:N11)</f>
         <v>3</v>
       </c>
     </row>
@@ -939,8 +939,8 @@
       <c r="D12" t="str">
         <v>mystery_ranch_nice_frame_load_sling</v>
       </c>
-      <c r="E12" t="str">
-        <v>trade offer</v>
+      <c r="E12">
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="N12">
+        <f>SUM(E12:M12)</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>SUM(F12:N12)</f>
         <v>4</v>
       </c>
     </row>
@@ -987,8 +987,8 @@
       <c r="D13" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E13" t="str">
-        <v>loot container</v>
+      <c r="E13">
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="N13">
+        <f>SUM(E13:M13)</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>SUM(F13:N13)</f>
         <v>5</v>
       </c>
     </row>
@@ -1035,8 +1035,8 @@
       <c r="D14" t="str">
         <v>black_herringbone</v>
       </c>
-      <c r="E14" t="str">
-        <v>hideout customization</v>
+      <c r="E14">
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1063,10 +1063,10 @@
         <v>0</v>
       </c>
       <c r="N14">
+        <f>SUM(E14:M14)</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f>SUM(F14:N14)</f>
         <v>7</v>
       </c>
     </row>
@@ -1083,8 +1083,8 @@
       <c r="D15" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E15" t="str">
-        <v>currency</v>
+      <c r="E15">
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="N15">
+        <f>SUM(E15:M15)</f>
         <v>0</v>
       </c>
       <c r="O15">
-        <f>SUM(F15:N15)</f>
         <v>5</v>
       </c>
     </row>
@@ -1131,8 +1131,8 @@
       <c r="D16" t="str">
         <v>heart</v>
       </c>
-      <c r="E16" t="str">
-        <v>pose</v>
+      <c r="E16">
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N16">
+        <f>SUM(E16:M16)</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>SUM(F16:N16)</f>
         <v>4</v>
       </c>
     </row>
@@ -1179,8 +1179,8 @@
       <c r="D17" t="str">
         <v>marked_dogtag_green</v>
       </c>
-      <c r="E17" t="str">
-        <v>dogtag</v>
+      <c r="E17">
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1207,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="N17">
+        <f>SUM(E17:M17)</f>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>SUM(F17:N17)</f>
         <v>5</v>
       </c>
     </row>
@@ -1227,8 +1227,8 @@
       <c r="D18" t="str">
         <v>microtech_jagdkommando_knife</v>
       </c>
-      <c r="E18" t="str">
-        <v>melee weapon</v>
+      <c r="E18">
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>0</v>
       </c>
       <c r="N18">
+        <f>SUM(E18:M18)</f>
         <v>0</v>
       </c>
       <c r="O18">
-        <f>SUM(F18:N18)</f>
         <v>10</v>
       </c>
     </row>
@@ -1275,8 +1275,8 @@
       <c r="D19" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E19" t="str">
-        <v>currency</v>
+      <c r="E19">
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1303,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="N19">
+        <f>SUM(E19:M19)</f>
         <v>0</v>
       </c>
       <c r="O19">
-        <f>SUM(F19:N19)</f>
         <v>5</v>
       </c>
     </row>
@@ -1323,8 +1323,8 @@
       <c r="D20" t="str">
         <v>beware_the_bear_poster</v>
       </c>
-      <c r="E20" t="str">
-        <v>poster</v>
+      <c r="E20">
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1351,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="N20">
+        <f>SUM(E20:M20)</f>
         <v>0</v>
       </c>
       <c r="O20">
-        <f>SUM(F20:N20)</f>
         <v>5</v>
       </c>
     </row>
@@ -1371,8 +1371,8 @@
       <c r="D21" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E21" t="str">
-        <v>loot container</v>
+      <c r="E21">
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1399,10 +1399,10 @@
         <v>0</v>
       </c>
       <c r="N21">
+        <f>SUM(E21:M21)</f>
         <v>0</v>
       </c>
       <c r="O21">
-        <f>SUM(F21:N21)</f>
         <v>5</v>
       </c>
     </row>
@@ -1419,8 +1419,8 @@
       <c r="D22" t="str">
         <v>orange_hawaii</v>
       </c>
-      <c r="E22" t="str">
-        <v>tactical clothing</v>
+      <c r="E22">
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1447,10 +1447,10 @@
         <v>0</v>
       </c>
       <c r="N22">
+        <f>SUM(E22:M22)</f>
         <v>0</v>
       </c>
       <c r="O22">
-        <f>SUM(F22:N22)</f>
         <v>10</v>
       </c>
     </row>
@@ -1467,8 +1467,8 @@
       <c r="D23" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E23" t="str">
-        <v>currency</v>
+      <c r="E23">
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>0</v>
       </c>
       <c r="N23">
+        <f>SUM(E23:M23)</f>
         <v>0</v>
       </c>
       <c r="O23">
-        <f>SUM(F23:N23)</f>
         <v>7</v>
       </c>
     </row>
@@ -1515,8 +1515,8 @@
       <c r="D24" t="str">
         <v>black_division_target</v>
       </c>
-      <c r="E24" t="str">
-        <v>hideout customization</v>
+      <c r="E24">
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="N24">
+        <f>SUM(E24:M24)</f>
         <v>0</v>
       </c>
       <c r="O24">
-        <f>SUM(F24:N24)</f>
         <v>5</v>
       </c>
     </row>
@@ -1563,8 +1563,8 @@
       <c r="D25" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E25" t="str">
-        <v>loot container</v>
+      <c r="E25">
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1591,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="N25">
+        <f>SUM(E25:M25)</f>
         <v>0</v>
       </c>
       <c r="O25">
-        <f>SUM(F25:N25)</f>
         <v>6</v>
       </c>
     </row>
@@ -1611,8 +1611,8 @@
       <c r="D26" t="str">
         <v>ferro_concepts_fcpc_5_plate_carrier_black_division</v>
       </c>
-      <c r="E26" t="str">
-        <v>trade offer</v>
+      <c r="E26">
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1639,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="N26">
+        <f>SUM(E26:M26)</f>
         <v>0</v>
       </c>
       <c r="O26">
-        <f>SUM(F26:N26)</f>
         <v>7</v>
       </c>
     </row>
@@ -1659,8 +1659,8 @@
       <c r="D27" t="str">
         <v>knyazev</v>
       </c>
-      <c r="E27" t="str">
-        <v>pmc face</v>
+      <c r="E27">
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1687,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="N27">
+        <f>SUM(E27:M27)</f>
         <v>0</v>
       </c>
       <c r="O27">
-        <f>SUM(F27:N27)</f>
         <v>13</v>
       </c>
     </row>
@@ -1707,8 +1707,8 @@
       <c r="D28" t="str">
         <v>oconnor</v>
       </c>
-      <c r="E28" t="str">
-        <v>pmc face</v>
+      <c r="E28">
+        <v>0</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>0</v>
       </c>
       <c r="N28">
+        <f>SUM(E28:M28)</f>
         <v>0</v>
       </c>
       <c r="O28">
-        <f>SUM(F28:N28)</f>
         <v>12</v>
       </c>
     </row>
@@ -1755,8 +1755,8 @@
       <c r="D29" t="str">
         <v>howa_type_20_5.56x45_assault_rifle</v>
       </c>
-      <c r="E29" t="str">
-        <v>trade offer</v>
+      <c r="E29">
+        <v>0</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="N29">
+        <f>SUM(E29:M29)</f>
         <v>0</v>
       </c>
       <c r="O29">
-        <f>SUM(F29:N29)</f>
         <v>11</v>
       </c>
     </row>
@@ -1803,8 +1803,8 @@
       <c r="D30" t="str">
         <v>marked_dogtag_red</v>
       </c>
-      <c r="E30" t="str">
-        <v>dogtag</v>
+      <c r="E30">
+        <v>0</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="N30">
+        <f>SUM(E30:M30)</f>
         <v>0</v>
       </c>
       <c r="O30">
-        <f>SUM(F30:N30)</f>
         <v>10</v>
       </c>
     </row>
@@ -1851,8 +1851,8 @@
       <c r="D31" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E31" t="str">
-        <v>currency</v>
+      <c r="E31">
+        <v>0</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1879,10 +1879,10 @@
         <v>0</v>
       </c>
       <c r="N31">
+        <f>SUM(E31:M31)</f>
         <v>0</v>
       </c>
       <c r="O31">
-        <f>SUM(F31:N31)</f>
         <v>9</v>
       </c>
     </row>
@@ -1899,8 +1899,8 @@
       <c r="D32" t="str">
         <v>scorpion_upper</v>
       </c>
-      <c r="E32" t="str">
-        <v>tactical clothing</v>
+      <c r="E32">
+        <v>0</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1927,10 +1927,10 @@
         <v>0</v>
       </c>
       <c r="N32">
+        <f>SUM(E32:M32)</f>
         <v>0</v>
       </c>
       <c r="O32">
-        <f>SUM(F32:N32)</f>
         <v>13</v>
       </c>
     </row>
@@ -1947,8 +1947,8 @@
       <c r="D33" t="str">
         <v>scorpion_lower</v>
       </c>
-      <c r="E33" t="str">
-        <v>tactical clothing</v>
+      <c r="E33">
+        <v>0</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1975,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="N33">
+        <f>SUM(E33:M33)</f>
         <v>0</v>
       </c>
       <c r="O33">
-        <f>SUM(F33:N33)</f>
         <v>13</v>
       </c>
     </row>
@@ -1995,8 +1995,8 @@
       <c r="D34" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E34" t="str">
-        <v>loot container</v>
+      <c r="E34">
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="N34">
+        <f>SUM(E34:M34)</f>
         <v>0</v>
       </c>
       <c r="O34">
-        <f>SUM(F34:N34)</f>
         <v>6</v>
       </c>
     </row>
@@ -2043,8 +2043,8 @@
       <c r="D35" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E35" t="str">
-        <v>currency</v>
+      <c r="E35">
+        <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2071,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="N35">
+        <f>SUM(E35:M35)</f>
         <v>0</v>
       </c>
       <c r="O35">
-        <f>SUM(F35:N35)</f>
         <v>14</v>
       </c>
     </row>
@@ -2091,8 +2091,8 @@
       <c r="D36" t="str">
         <v>white_accent_walls</v>
       </c>
-      <c r="E36" t="str">
-        <v>hideout customization</v>
+      <c r="E36">
+        <v>0</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="N36">
+        <f>SUM(E36:M36)</f>
         <v>0</v>
       </c>
       <c r="O36">
-        <f>SUM(F36:N36)</f>
         <v>13</v>
       </c>
     </row>
@@ -2139,8 +2139,8 @@
       <c r="D37" t="str">
         <v>arch</v>
       </c>
-      <c r="E37" t="str">
-        <v>pose</v>
+      <c r="E37">
+        <v>0</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="N37">
+        <f>SUM(E37:M37)</f>
         <v>0</v>
       </c>
       <c r="O37">
-        <f>SUM(F37:N37)</f>
         <v>6</v>
       </c>
     </row>
@@ -2187,8 +2187,8 @@
       <c r="D38" t="str">
         <v>dome</v>
       </c>
-      <c r="E38" t="str">
-        <v>pose</v>
+      <c r="E38">
+        <v>0</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2215,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="N38">
+        <f>SUM(E38:M38)</f>
         <v>0</v>
       </c>
       <c r="O38">
-        <f>SUM(F38:N38)</f>
         <v>4</v>
       </c>
     </row>
@@ -2235,8 +2235,8 @@
       <c r="D39" t="str">
         <v>spiritus_systems_lv-119_plate_carrier_black_division_v2</v>
       </c>
-      <c r="E39" t="str">
-        <v>trade offer</v>
+      <c r="E39">
+        <v>0</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="N39">
+        <f>SUM(E39:M39)</f>
         <v>0</v>
       </c>
       <c r="O39">
-        <f>SUM(F39:N39)</f>
         <v>12</v>
       </c>
     </row>
@@ -2283,8 +2283,8 @@
       <c r="D40" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E40" t="str">
-        <v>currency</v>
+      <c r="E40">
+        <v>0</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="N40">
+        <f>SUM(E40:M40)</f>
         <v>0</v>
       </c>
       <c r="O40">
-        <f>SUM(F40:N40)</f>
         <v>6</v>
       </c>
     </row>
@@ -2331,8 +2331,8 @@
       <c r="D41" t="str">
         <v>tasmanian_tiger_modular_pack_45_plus_multicam_black</v>
       </c>
-      <c r="E41" t="str">
-        <v>trade offer</v>
+      <c r="E41">
+        <v>0</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2359,10 +2359,10 @@
         <v>0</v>
       </c>
       <c r="N41">
+        <f>SUM(E41:M41)</f>
         <v>0</v>
       </c>
       <c r="O41">
-        <f>SUM(F41:N41)</f>
         <v>9</v>
       </c>
     </row>
@@ -2379,8 +2379,8 @@
       <c r="D42" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E42" t="str">
-        <v>loot container</v>
+      <c r="E42">
+        <v>0</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="N42">
+        <f>SUM(E42:M42)</f>
         <v>0</v>
       </c>
       <c r="O42">
-        <f>SUM(F42:N42)</f>
         <v>5</v>
       </c>
     </row>
@@ -2427,8 +2427,8 @@
       <c r="D43" t="str">
         <v>server_room</v>
       </c>
-      <c r="E43" t="str">
-        <v>main menu background</v>
+      <c r="E43">
+        <v>0</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2455,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="N43">
+        <f>SUM(E43:M43)</f>
         <v>0</v>
       </c>
       <c r="O43">
-        <f>SUM(F43:N43)</f>
         <v>18</v>
       </c>
     </row>
@@ -2475,8 +2475,8 @@
       <c r="D44" t="str">
         <v>anton</v>
       </c>
-      <c r="E44" t="str">
-        <v>pmc voice</v>
+      <c r="E44">
+        <v>0</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2503,10 +2503,10 @@
         <v>0</v>
       </c>
       <c r="N44">
+        <f>SUM(E44:M44)</f>
         <v>0</v>
       </c>
       <c r="O44">
-        <f>SUM(F44:N44)</f>
         <v>20</v>
       </c>
     </row>
@@ -2523,8 +2523,8 @@
       <c r="D45" t="str">
         <v>garrett</v>
       </c>
-      <c r="E45" t="str">
-        <v>pmc voice</v>
+      <c r="E45">
+        <v>0</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2551,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="N45">
+        <f>SUM(E45:M45)</f>
         <v>0</v>
       </c>
       <c r="O45">
-        <f>SUM(F45:N45)</f>
         <v>20</v>
       </c>
     </row>
@@ -2571,8 +2571,8 @@
       <c r="D46" t="str">
         <v>black_division_gear_crate</v>
       </c>
-      <c r="E46" t="str">
-        <v>loot container</v>
+      <c r="E46">
+        <v>0</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2599,10 +2599,10 @@
         <v>0</v>
       </c>
       <c r="N46">
+        <f>SUM(E46:M46)</f>
         <v>0</v>
       </c>
       <c r="O46">
-        <f>SUM(F46:N46)</f>
         <v>7</v>
       </c>
     </row>
@@ -2619,8 +2619,8 @@
       <c r="D47" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E47" t="str">
-        <v>currency</v>
+      <c r="E47">
+        <v>0</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2647,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="N47">
+        <f>SUM(E47:M47)</f>
         <v>0</v>
       </c>
       <c r="O47">
-        <f>SUM(F47:N47)</f>
         <v>13</v>
       </c>
     </row>
@@ -2667,8 +2667,8 @@
       <c r="D48" t="str">
         <v>marked_dogtag_red_bullet_hole</v>
       </c>
-      <c r="E48" t="str">
-        <v>dogtag</v>
+      <c r="E48">
+        <v>0</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="N48">
+        <f>SUM(E48:M48)</f>
         <v>0</v>
       </c>
       <c r="O48">
-        <f>SUM(F48:N48)</f>
         <v>11</v>
       </c>
     </row>
@@ -2715,8 +2715,8 @@
       <c r="D49" t="str">
         <v>tarcoin</v>
       </c>
-      <c r="E49" t="str">
-        <v>currency</v>
+      <c r="E49">
+        <v>0</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2743,10 +2743,10 @@
         <v>0</v>
       </c>
       <c r="N49">
+        <f>SUM(E49:M49)</f>
         <v>0</v>
       </c>
       <c r="O49">
-        <f>SUM(F49:N49)</f>
         <v>16</v>
       </c>
     </row>
@@ -2763,8 +2763,8 @@
       <c r="D50" t="str">
         <v>knyazev_after_battle</v>
       </c>
-      <c r="E50" t="str">
-        <v>pmc face</v>
+      <c r="E50">
+        <v>0</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="N50">
+        <f>SUM(E50:M50)</f>
         <v>0</v>
       </c>
       <c r="O50">
-        <f>SUM(F50:N50)</f>
         <v>19</v>
       </c>
     </row>
@@ -2811,8 +2811,8 @@
       <c r="D51" t="str">
         <v>oconnor_after_battle</v>
       </c>
-      <c r="E51" t="str">
-        <v>pmc face</v>
+      <c r="E51">
+        <v>0</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2839,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="N51">
+        <f>SUM(E51:M51)</f>
         <v>0</v>
       </c>
       <c r="O51">
-        <f>SUM(F51:N51)</f>
         <v>19</v>
       </c>
     </row>
@@ -2859,8 +2859,8 @@
       <c r="D52" t="str">
         <v>norinco_qbz-191_5.8x42_assault_rifle</v>
       </c>
-      <c r="E52" t="str">
-        <v>trade offer</v>
+      <c r="E52">
+        <v>0</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2887,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="N52">
+        <f>SUM(E52:M52)</f>
         <v>0</v>
       </c>
       <c r="O52">
-        <f>SUM(F52:N52)</f>
         <v>29</v>
       </c>
     </row>
@@ -2907,8 +2907,8 @@
       <c r="D53" t="str">
         <v>nocturnal_upper</v>
       </c>
-      <c r="E53" t="str">
-        <v>tactical clothing</v>
+      <c r="E53">
+        <v>0</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="N53">
+        <f>SUM(E53:M53)</f>
         <v>0</v>
       </c>
       <c r="O53">
-        <f>SUM(F53:N53)</f>
         <v>25</v>
       </c>
     </row>
@@ -2955,8 +2955,8 @@
       <c r="D54" t="str">
         <v>nocturnal_lower</v>
       </c>
-      <c r="E54" t="str">
-        <v>tactical clothing</v>
+      <c r="E54">
+        <v>0</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2983,50 +2983,16 @@
         <v>0</v>
       </c>
       <c r="N54">
+        <f>SUM(E54:M54)</f>
         <v>0</v>
       </c>
       <c r="O54">
-        <f>SUM(F54:N54)</f>
         <v>23</v>
       </c>
     </row>
-    <row r="55">
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <f>SUM(O2:O54)</f>
-        <v>501</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O54"/>
   </ignoredErrors>
 </worksheet>
 </file>